--- a/Models/Лошади/Датасет по лошадям wide.xlsx
+++ b/Models/Лошади/Датасет по лошадям wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>8733.529999999999</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1610.32</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1632.1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>549.47</v>
+      </c>
+      <c r="E122" t="n">
+        <v>555.2</v>
+      </c>
+      <c r="F122" t="n">
+        <v>694.36</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>5</v>
+      </c>
+      <c r="I122" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1469.9</v>
+      </c>
+      <c r="K122" t="n">
+        <v>802.51</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1336.21</v>
+      </c>
+      <c r="M122" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="N122" t="n">
+        <v>821.5</v>
+      </c>
+      <c r="O122" t="n">
+        <v>90.89999999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>1165.51</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1237.31</v>
+      </c>
+      <c r="R122" t="n">
+        <v>2126</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1631.78</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1080.05</v>
+      </c>
+      <c r="U122" t="n">
+        <v>2598.76</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1067</v>
+      </c>
+      <c r="C123" t="n">
+        <v>834.4499999999999</v>
+      </c>
+      <c r="D123" t="n">
+        <v>727.1799999999999</v>
+      </c>
+      <c r="E123" t="n">
+        <v>934.8</v>
+      </c>
+      <c r="F123" t="n">
+        <v>910.6300000000001</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I123" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J123" t="n">
+        <v>903.7</v>
+      </c>
+      <c r="K123" t="n">
+        <v>900.05</v>
+      </c>
+      <c r="L123" t="n">
+        <v>779.29</v>
+      </c>
+      <c r="M123" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="N123" t="n">
+        <v>819.0700000000001</v>
+      </c>
+      <c r="O123" t="n">
+        <v>123.95</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1732.91</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1032.43</v>
+      </c>
+      <c r="R123" t="n">
+        <v>413.5</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1565.58</v>
+      </c>
+      <c r="T123" t="n">
+        <v>307.15</v>
+      </c>
+      <c r="U123" t="n">
+        <v>2732.23</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1190.29</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1715.21</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3248.83</v>
+      </c>
+      <c r="E124" t="n">
+        <v>877.25</v>
+      </c>
+      <c r="F124" t="n">
+        <v>592.5700000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I124" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1540.2</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1034.46</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1358.98</v>
+      </c>
+      <c r="M124" t="n">
+        <v>366.41</v>
+      </c>
+      <c r="N124" t="n">
+        <v>758.6600000000001</v>
+      </c>
+      <c r="O124" t="n">
+        <v>205.05</v>
+      </c>
+      <c r="P124" t="n">
+        <v>2347.51</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1470.26</v>
+      </c>
+      <c r="R124" t="n">
+        <v>795.3000000000001</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1804.74</v>
+      </c>
+      <c r="T124" t="n">
+        <v>569.05</v>
+      </c>
+      <c r="U124" t="n">
+        <v>2726.66</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>936.8199999999999</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1757.48</v>
+      </c>
+      <c r="D125" t="n">
+        <v>978.78</v>
+      </c>
+      <c r="E125" t="n">
+        <v>667.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1041.58</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>962.22</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1049.59</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1678.28</v>
+      </c>
+      <c r="M125" t="n">
+        <v>216.41</v>
+      </c>
+      <c r="N125" t="n">
+        <v>872.49</v>
+      </c>
+      <c r="O125" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="P125" t="n">
+        <v>2583.73</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="R125" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1533.22</v>
+      </c>
+      <c r="T125" t="n">
+        <v>522.74</v>
+      </c>
+      <c r="U125" t="n">
+        <v>2579.69</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1068.99</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1457.7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>787.7</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1008.2</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1239.36</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I126" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1000.72</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1322.31</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1214.16</v>
+      </c>
+      <c r="N126" t="n">
+        <v>578.73</v>
+      </c>
+      <c r="O126" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="P126" t="n">
+        <v>3180.08</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>372.01</v>
+      </c>
+      <c r="R126" t="n">
+        <v>415.8</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1589.3</v>
+      </c>
+      <c r="T126" t="n">
+        <v>506.27</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1902.11</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2008.72</v>
+      </c>
+      <c r="C127" t="n">
+        <v>2493.35</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2309.5</v>
+      </c>
+      <c r="E127" t="n">
+        <v>720.25</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2347.63</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I127" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J127" t="n">
+        <v>2182.3</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1661.76</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3725.33</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1154.83</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1190.92</v>
+      </c>
+      <c r="O127" t="n">
+        <v>305.8</v>
+      </c>
+      <c r="P127" t="n">
+        <v>5805.7</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>3180.35</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1513.7</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3332.59</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1524.19</v>
+      </c>
+      <c r="U127" t="n">
+        <v>2208.35</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1050.06</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1468.96</v>
+      </c>
+      <c r="D128" t="n">
+        <v>910.76</v>
+      </c>
+      <c r="E128" t="n">
+        <v>492.3000000000001</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1570.65</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I128" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="K128" t="n">
+        <v>642.3200000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>873.8399999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>250.09</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1070.66</v>
+      </c>
+      <c r="O128" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="P128" t="n">
+        <v>6077.3</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>264.57</v>
+      </c>
+      <c r="R128" t="n">
+        <v>751.7</v>
+      </c>
+      <c r="S128" t="n">
+        <v>2325.81</v>
+      </c>
+      <c r="T128" t="n">
+        <v>2030.74</v>
+      </c>
+      <c r="U128" t="n">
+        <v>2272.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
